--- a/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA829533</t>
+          <t xml:space="preserve">CARGA114098</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA114098</t>
+          <t xml:space="preserve">CARGA617068</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
+++ b/Plantillas_carga_masiva/Republica_Dominicana/Estructura_Cargue_Masivo_Instrumentos.xlsx
@@ -138,7 +138,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CARGA617068</t>
+          <t xml:space="preserve">CARGA765203</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
